--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -577,7 +577,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/29</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -704,45 +704,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -788,7 +788,7 @@
       <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -839,7 +839,7 @@
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -890,7 +890,7 @@
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
@@ -941,7 +941,7 @@
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -994,7 +994,7 @@
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.6%</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       <c r="G11" s="6" t="inlineStr"/>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1090,7 +1090,7 @@
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="G13" s="6" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1181,7 +1181,7 @@
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="M15" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N15" s="5" t="n">
         <v>27</v>
@@ -1297,10 +1297,10 @@
         <v>2</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1375,10 +1375,10 @@
         <v>2</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       <c r="G17" s="6" t="inlineStr"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1453,10 +1453,10 @@
         <v>2</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1531,10 +1531,10 @@
         <v>2</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1609,10 +1609,10 @@
         <v>2</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1687,10 +1687,10 @@
         <v>2</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1815,7 +1815,7 @@
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1893,7 +1893,7 @@
       <c r="G23" s="6" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1971,7 +1971,7 @@
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -2049,7 +2049,7 @@
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="M25" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>27</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -2205,7 +2205,7 @@
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -2430,45 +2430,45 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -3629,45 +3629,45 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4798,45 +4798,45 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5967,45 +5967,45 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr"/>
-      <c r="H113" s="6" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7136,45 +7136,45 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>24/32</t>
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>20/32</t>
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>23/32</t>
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr">
@@ -13034,7 +13034,7 @@
       <c r="G275" s="6" t="inlineStr"/>
       <c r="H275" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I275" s="6" t="inlineStr">
@@ -13077,7 +13077,7 @@
       <c r="G276" s="6" t="inlineStr"/>
       <c r="H276" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I276" s="6" t="inlineStr">
@@ -13120,7 +13120,7 @@
       <c r="G277" s="6" t="inlineStr"/>
       <c r="H277" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I277" s="6" t="inlineStr">
@@ -13163,7 +13163,7 @@
       <c r="G278" s="6" t="inlineStr"/>
       <c r="H278" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I278" s="6" t="inlineStr">
@@ -13206,7 +13206,7 @@
       <c r="G279" s="6" t="inlineStr"/>
       <c r="H279" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I279" s="6" t="inlineStr">
@@ -13249,7 +13249,7 @@
       <c r="G280" s="6" t="inlineStr"/>
       <c r="H280" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I280" s="6" t="inlineStr">
@@ -13292,7 +13292,7 @@
       <c r="G281" s="6" t="inlineStr"/>
       <c r="H281" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I281" s="6" t="inlineStr">
@@ -13335,7 +13335,7 @@
       <c r="G282" s="6" t="inlineStr"/>
       <c r="H282" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I282" s="6" t="inlineStr">
@@ -13378,7 +13378,7 @@
       <c r="G283" s="6" t="inlineStr"/>
       <c r="H283" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I283" s="6" t="inlineStr">
@@ -13421,7 +13421,7 @@
       <c r="G284" s="6" t="inlineStr"/>
       <c r="H284" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I284" s="6" t="inlineStr">
@@ -13464,7 +13464,7 @@
       <c r="G285" s="6" t="inlineStr"/>
       <c r="H285" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I285" s="6" t="inlineStr">
@@ -13507,7 +13507,7 @@
       <c r="G286" s="6" t="inlineStr"/>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
@@ -13550,7 +13550,7 @@
       <c r="G287" s="6" t="inlineStr"/>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
@@ -13593,7 +13593,7 @@
       <c r="G288" s="6" t="inlineStr"/>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
@@ -13636,7 +13636,7 @@
       <c r="G289" s="6" t="inlineStr"/>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
@@ -13679,7 +13679,7 @@
       <c r="G290" s="6" t="inlineStr"/>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
@@ -13722,7 +13722,7 @@
       <c r="G291" s="6" t="inlineStr"/>
       <c r="H291" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I291" s="6" t="inlineStr">
@@ -13765,7 +13765,7 @@
       <c r="G292" s="6" t="inlineStr"/>
       <c r="H292" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I292" s="6" t="inlineStr">
@@ -13808,7 +13808,7 @@
       <c r="G293" s="6" t="inlineStr"/>
       <c r="H293" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I293" s="6" t="inlineStr">
@@ -13851,7 +13851,7 @@
       <c r="G294" s="6" t="inlineStr"/>
       <c r="H294" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I294" s="6" t="inlineStr">
@@ -13894,7 +13894,7 @@
       <c r="G295" s="6" t="inlineStr"/>
       <c r="H295" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I295" s="6" t="inlineStr">
@@ -13937,7 +13937,7 @@
       <c r="G296" s="6" t="inlineStr"/>
       <c r="H296" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I296" s="6" t="inlineStr">
@@ -13980,7 +13980,7 @@
       <c r="G297" s="6" t="inlineStr"/>
       <c r="H297" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
@@ -14023,7 +14023,7 @@
       <c r="G298" s="6" t="inlineStr"/>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>29/31</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/31</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>16/31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/31</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7">
@@ -855,7 +855,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -910,7 +910,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>16/31</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>28/31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/31</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>27</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>27</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>27</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>27</v>
@@ -1711,7 +1711,7 @@
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>27</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1808,28 +1808,28 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
         <v>15</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>27</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="M23" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>27</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>27</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2120,28 +2120,28 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>30/30</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>26/30</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>24/30</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/30</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/30</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/30</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/30</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/30</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>29/30</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -4377,7 +4377,7 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -4420,7 +4420,7 @@
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -4463,7 +4463,7 @@
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -4506,7 +4506,7 @@
       <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -4549,7 +4549,7 @@
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -4592,7 +4592,7 @@
       <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -4635,7 +4635,7 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -4678,7 +4678,7 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -4721,7 +4721,7 @@
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -4807,7 +4807,7 @@
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>28/28</t>
+          <t>28/30</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>24/30</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>14/30</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>14/30</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>15/30</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
@@ -5598,7 +5598,7 @@
       <c r="G99" s="5" t="inlineStr"/>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
@@ -5641,7 +5641,7 @@
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
@@ -5684,7 +5684,7 @@
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -5770,7 +5770,7 @@
       <c r="G103" s="5" t="inlineStr"/>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="G104" s="5" t="inlineStr"/>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
@@ -5856,7 +5856,7 @@
       <c r="G105" s="5" t="inlineStr"/>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -5899,7 +5899,7 @@
       <c r="G106" s="5" t="inlineStr"/>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
@@ -5942,7 +5942,7 @@
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -5985,7 +5985,7 @@
       <c r="G108" s="5" t="inlineStr"/>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       <c r="G109" s="5" t="inlineStr"/>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>30/30</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/30</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/30</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>17/30</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>29/30</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -6819,7 +6819,7 @@
       <c r="G126" s="5" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -6862,7 +6862,7 @@
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
@@ -6905,7 +6905,7 @@
       <c r="G128" s="5" t="inlineStr"/>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
@@ -6948,7 +6948,7 @@
       <c r="G129" s="5" t="inlineStr"/>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
@@ -6991,7 +6991,7 @@
       <c r="G130" s="5" t="inlineStr"/>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
@@ -7034,7 +7034,7 @@
       <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
@@ -7077,7 +7077,7 @@
       <c r="G132" s="5" t="inlineStr"/>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
@@ -7120,7 +7120,7 @@
       <c r="G133" s="5" t="inlineStr"/>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -7163,7 +7163,7 @@
       <c r="G134" s="5" t="inlineStr"/>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -7206,7 +7206,7 @@
       <c r="G135" s="5" t="inlineStr"/>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
@@ -7249,7 +7249,7 @@
       <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/30</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/30</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/30</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/30</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/30</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -7997,7 +7997,7 @@
       <c r="G152" s="5" t="inlineStr"/>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
@@ -8040,7 +8040,7 @@
       <c r="G153" s="5" t="inlineStr"/>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
@@ -8083,7 +8083,7 @@
       <c r="G154" s="5" t="inlineStr"/>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -8126,7 +8126,7 @@
       <c r="G155" s="5" t="inlineStr"/>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I155" s="5" t="inlineStr">
@@ -8169,7 +8169,7 @@
       <c r="G156" s="5" t="inlineStr"/>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       <c r="G157" s="5" t="inlineStr"/>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
@@ -8255,7 +8255,7 @@
       <c r="G158" s="5" t="inlineStr"/>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
@@ -8298,7 +8298,7 @@
       <c r="G159" s="5" t="inlineStr"/>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
@@ -8341,7 +8341,7 @@
       <c r="G160" s="5" t="inlineStr"/>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
@@ -8384,7 +8384,7 @@
       <c r="G161" s="5" t="inlineStr"/>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I161" s="5" t="inlineStr">
@@ -8427,7 +8427,7 @@
       <c r="G162" s="5" t="inlineStr"/>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I162" s="5" t="inlineStr">
@@ -8470,7 +8470,7 @@
       <c r="G163" s="5" t="inlineStr"/>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I163" s="5" t="inlineStr">
@@ -8480,707 +8480,647 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="9" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>19/29</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="inlineStr"/>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="9" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>18/29</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="inlineStr"/>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E166" s="9" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>17/29</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="inlineStr"/>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="9" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>16/29</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr"/>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E168" s="9" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>12/29</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr"/>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E169" s="9" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>14/29</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr"/>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E170" s="9" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>13/29</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr"/>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E171" s="9" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>13/29</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="inlineStr"/>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E172" s="9" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>13/29</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="9" t="inlineStr"/>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="9" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>13/29</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr"/>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="9" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>8/29</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr"/>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E175" s="9" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>29/29</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr"/>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E176" s="9" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr"/>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E177" s="9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="9" t="inlineStr"/>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E178" s="9" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>25/29</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr"/>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9158,7 @@
       <c r="G179" s="5" t="inlineStr"/>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
@@ -9261,7 +9201,7 @@
       <c r="G180" s="5" t="inlineStr"/>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
@@ -9304,7 +9244,7 @@
       <c r="G181" s="5" t="inlineStr"/>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
@@ -9347,7 +9287,7 @@
       <c r="G182" s="5" t="inlineStr"/>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
@@ -9390,7 +9330,7 @@
       <c r="G183" s="5" t="inlineStr"/>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
@@ -9433,7 +9373,7 @@
       <c r="G184" s="5" t="inlineStr"/>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
@@ -9476,7 +9416,7 @@
       <c r="G185" s="5" t="inlineStr"/>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
@@ -9519,7 +9459,7 @@
       <c r="G186" s="5" t="inlineStr"/>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
@@ -9562,7 +9502,7 @@
       <c r="G187" s="5" t="inlineStr"/>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
@@ -9605,7 +9545,7 @@
       <c r="G188" s="5" t="inlineStr"/>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
@@ -9648,7 +9588,7 @@
       <c r="G189" s="5" t="inlineStr"/>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
@@ -9691,7 +9631,7 @@
       <c r="G190" s="5" t="inlineStr"/>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I190" s="5" t="inlineStr">
@@ -9738,7 +9678,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>18/32</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -9785,7 +9725,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -9832,7 +9772,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>17/30</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -9879,7 +9819,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>12/30</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -9926,7 +9866,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>11/32</t>
+          <t>11/30</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -9973,7 +9913,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>11/30</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -10020,7 +9960,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>15/30</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -10067,7 +10007,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>14/32</t>
+          <t>13/30</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -10114,7 +10054,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>13/32</t>
+          <t>10/30</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -10161,7 +10101,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>13/30</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -10208,7 +10148,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>10/32</t>
+          <t>7/30</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -10255,7 +10195,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>29/30</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -10302,7 +10242,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>28/32</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
@@ -10349,7 +10289,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>28/32</t>
+          <t>26/30</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
@@ -10396,7 +10336,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
@@ -10439,7 +10379,7 @@
       <c r="G206" s="5" t="inlineStr"/>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I206" s="5" t="inlineStr">
@@ -10482,7 +10422,7 @@
       <c r="G207" s="5" t="inlineStr"/>
       <c r="H207" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I207" s="5" t="inlineStr">
@@ -10525,7 +10465,7 @@
       <c r="G208" s="5" t="inlineStr"/>
       <c r="H208" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I208" s="5" t="inlineStr">
@@ -10568,7 +10508,7 @@
       <c r="G209" s="5" t="inlineStr"/>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I209" s="5" t="inlineStr">
@@ -10611,7 +10551,7 @@
       <c r="G210" s="5" t="inlineStr"/>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I210" s="5" t="inlineStr">
@@ -10654,7 +10594,7 @@
       <c r="G211" s="5" t="inlineStr"/>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I211" s="5" t="inlineStr">
@@ -10697,7 +10637,7 @@
       <c r="G212" s="5" t="inlineStr"/>
       <c r="H212" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I212" s="5" t="inlineStr">
@@ -10740,7 +10680,7 @@
       <c r="G213" s="5" t="inlineStr"/>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
@@ -10783,7 +10723,7 @@
       <c r="G214" s="5" t="inlineStr"/>
       <c r="H214" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I214" s="5" t="inlineStr">
@@ -10826,7 +10766,7 @@
       <c r="G215" s="5" t="inlineStr"/>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I215" s="5" t="inlineStr">
@@ -10869,7 +10809,7 @@
       <c r="G216" s="5" t="inlineStr"/>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I216" s="5" t="inlineStr">
@@ -10912,7 +10852,7 @@
       <c r="G217" s="5" t="inlineStr"/>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I217" s="5" t="inlineStr">
@@ -10959,7 +10899,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -11006,7 +10946,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
@@ -11053,7 +10993,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
@@ -11100,7 +11040,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
@@ -11147,7 +11087,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
@@ -11194,7 +11134,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
@@ -11241,7 +11181,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
@@ -11288,7 +11228,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
@@ -11335,7 +11275,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
@@ -11382,7 +11322,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
@@ -11429,7 +11369,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
@@ -11476,7 +11416,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>29/30</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
@@ -11523,7 +11463,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
@@ -11570,7 +11510,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -11617,7 +11557,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
@@ -11660,7 +11600,7 @@
       <c r="G233" s="5" t="inlineStr"/>
       <c r="H233" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I233" s="5" t="inlineStr">
@@ -11703,7 +11643,7 @@
       <c r="G234" s="5" t="inlineStr"/>
       <c r="H234" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I234" s="5" t="inlineStr">
@@ -11746,7 +11686,7 @@
       <c r="G235" s="5" t="inlineStr"/>
       <c r="H235" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I235" s="5" t="inlineStr">
@@ -11789,7 +11729,7 @@
       <c r="G236" s="5" t="inlineStr"/>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I236" s="5" t="inlineStr">
@@ -11832,7 +11772,7 @@
       <c r="G237" s="5" t="inlineStr"/>
       <c r="H237" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I237" s="5" t="inlineStr">
@@ -11875,7 +11815,7 @@
       <c r="G238" s="5" t="inlineStr"/>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I238" s="5" t="inlineStr">
@@ -11918,7 +11858,7 @@
       <c r="G239" s="5" t="inlineStr"/>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I239" s="5" t="inlineStr">
@@ -11961,7 +11901,7 @@
       <c r="G240" s="5" t="inlineStr"/>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
@@ -12004,7 +11944,7 @@
       <c r="G241" s="5" t="inlineStr"/>
       <c r="H241" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I241" s="5" t="inlineStr">
@@ -12047,7 +11987,7 @@
       <c r="G242" s="5" t="inlineStr"/>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I242" s="5" t="inlineStr">
@@ -12090,7 +12030,7 @@
       <c r="G243" s="5" t="inlineStr"/>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I243" s="5" t="inlineStr">
@@ -12133,7 +12073,7 @@
       <c r="G244" s="5" t="inlineStr"/>
       <c r="H244" s="5" t="inlineStr">
         <is>
-          <t>0/29</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I244" s="5" t="inlineStr">
@@ -12180,7 +12120,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
@@ -12227,7 +12167,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>24/30</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
@@ -12274,7 +12214,7 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
@@ -12321,7 +12261,7 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
@@ -12368,7 +12308,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/30</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
@@ -12415,7 +12355,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
@@ -12462,7 +12402,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
@@ -12509,7 +12449,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/30</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
@@ -12556,7 +12496,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
@@ -12603,7 +12543,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
@@ -12650,7 +12590,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>15/30</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
@@ -12697,7 +12637,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>30/30</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
@@ -12744,7 +12684,7 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
@@ -12791,7 +12731,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>26/30</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
@@ -12838,7 +12778,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
@@ -12881,7 +12821,7 @@
       <c r="G260" s="5" t="inlineStr"/>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
@@ -12924,7 +12864,7 @@
       <c r="G261" s="5" t="inlineStr"/>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I261" s="5" t="inlineStr">
@@ -12967,7 +12907,7 @@
       <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I262" s="5" t="inlineStr">
@@ -13010,7 +12950,7 @@
       <c r="G263" s="5" t="inlineStr"/>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I263" s="5" t="inlineStr">
@@ -13053,7 +12993,7 @@
       <c r="G264" s="5" t="inlineStr"/>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I264" s="5" t="inlineStr">
@@ -13096,7 +13036,7 @@
       <c r="G265" s="5" t="inlineStr"/>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I265" s="5" t="inlineStr">
@@ -13139,7 +13079,7 @@
       <c r="G266" s="5" t="inlineStr"/>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I266" s="5" t="inlineStr">
@@ -13182,7 +13122,7 @@
       <c r="G267" s="5" t="inlineStr"/>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I267" s="5" t="inlineStr">
@@ -13225,7 +13165,7 @@
       <c r="G268" s="5" t="inlineStr"/>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I268" s="5" t="inlineStr">
@@ -13268,7 +13208,7 @@
       <c r="G269" s="5" t="inlineStr"/>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I269" s="5" t="inlineStr">
@@ -13311,7 +13251,7 @@
       <c r="G270" s="5" t="inlineStr"/>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I270" s="5" t="inlineStr">
@@ -13354,7 +13294,7 @@
       <c r="G271" s="5" t="inlineStr"/>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I271" s="5" t="inlineStr">
@@ -13401,7 +13341,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -13448,7 +13388,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
@@ -13495,7 +13435,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>22/30</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
@@ -13542,7 +13482,7 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>24/32</t>
+          <t>23/30</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
@@ -13552,49 +13492,45 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B276" s="2" t="inlineStr">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B276" s="9" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="C276" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E276" s="9" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G276" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
-      <c r="H276" s="2" t="inlineStr">
-        <is>
-          <t>1/32</t>
-        </is>
-      </c>
-      <c r="I276" s="2" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F276" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G276" s="9" t="inlineStr"/>
+      <c r="H276" s="9" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I276" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13636,7 +13572,7 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
@@ -13683,7 +13619,7 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>24/30</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
@@ -13730,7 +13666,7 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>25/32</t>
+          <t>24/30</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
@@ -13777,7 +13713,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>21/32</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
@@ -13824,7 +13760,7 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>21/32</t>
+          <t>19/30</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
@@ -13871,7 +13807,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>18/32</t>
+          <t>16/30</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
@@ -13918,7 +13854,7 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>30/30</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
@@ -13965,7 +13901,7 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>29/32</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
@@ -14012,7 +13948,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>28/32</t>
+          <t>26/30</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
@@ -14059,7 +13995,7 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>28/32</t>
+          <t>26/30</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
@@ -14102,7 +14038,7 @@
       <c r="G287" s="5" t="inlineStr"/>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I287" s="5" t="inlineStr">
@@ -14145,7 +14081,7 @@
       <c r="G288" s="5" t="inlineStr"/>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
@@ -14188,7 +14124,7 @@
       <c r="G289" s="5" t="inlineStr"/>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I289" s="5" t="inlineStr">
@@ -14231,7 +14167,7 @@
       <c r="G290" s="5" t="inlineStr"/>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I290" s="5" t="inlineStr">
@@ -14274,7 +14210,7 @@
       <c r="G291" s="5" t="inlineStr"/>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I291" s="5" t="inlineStr">
@@ -14317,7 +14253,7 @@
       <c r="G292" s="5" t="inlineStr"/>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
@@ -14360,7 +14296,7 @@
       <c r="G293" s="5" t="inlineStr"/>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
@@ -14403,7 +14339,7 @@
       <c r="G294" s="5" t="inlineStr"/>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
@@ -14446,7 +14382,7 @@
       <c r="G295" s="5" t="inlineStr"/>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I295" s="5" t="inlineStr">
@@ -14489,7 +14425,7 @@
       <c r="G296" s="5" t="inlineStr"/>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I296" s="5" t="inlineStr">
@@ -14532,7 +14468,7 @@
       <c r="G297" s="5" t="inlineStr"/>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I297" s="5" t="inlineStr">
@@ -14575,7 +14511,7 @@
       <c r="G298" s="5" t="inlineStr"/>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I298" s="5" t="inlineStr">
@@ -14763,7 +14699,7 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
@@ -14853,7 +14789,7 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
@@ -14900,7 +14836,7 @@
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
@@ -14994,7 +14930,7 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
@@ -15041,7 +14977,7 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
@@ -15135,7 +15071,7 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>28/29</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
@@ -15182,7 +15118,7 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
@@ -15229,7 +15165,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
@@ -15276,7 +15212,7 @@
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -1502,65 +1502,69 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1580,22 +1584,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -1662,22 +1666,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -1740,22 +1744,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -1818,22 +1822,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1900,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -1974,22 +1978,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -2052,22 +2056,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2134,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -2208,22 +2212,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -3127,45 +3131,49 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4352,45 +4360,49 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5577,45 +5589,49 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>28/28</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6802,45 +6818,49 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8027,45 +8047,49 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E153" s="5" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr"/>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9209,45 +9233,49 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E179" s="5" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr"/>
-      <c r="H179" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10430,45 +10458,49 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B206" s="5" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D206" s="5" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E206" s="5" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr"/>
-      <c r="H206" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I206" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>29/32</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10983,7 +11015,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -11651,45 +11683,49 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr"/>
-      <c r="H233" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12872,45 +12908,49 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E260" s="5" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr"/>
-      <c r="H260" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I260" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>29/31</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14093,45 +14133,49 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C287" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D287" s="5" t="inlineStr">
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E287" s="5" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F287" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G287" s="5" t="inlineStr"/>
-      <c r="H287" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I287" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>27/32</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15310,45 +15354,49 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B314" s="5" t="inlineStr">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C314" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D314" s="5" t="inlineStr">
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E314" s="5" t="inlineStr">
+      <c r="E314" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F314" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G314" s="5" t="inlineStr"/>
-      <c r="H314" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I314" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -1936,45 +1936,49 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -2178,43 +2182,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2256,86 +2260,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2506,7 +2510,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2568,7 +2572,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2630,7 +2634,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3394,45 +3398,49 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3531,129 +3539,129 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4684,7 +4692,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>28/31</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4788,129 +4796,129 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5904,45 +5912,49 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6041,129 +6053,129 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7157,45 +7169,49 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7294,129 +7310,129 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8410,45 +8426,49 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E158" s="5" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr"/>
-      <c r="H158" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I158" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8547,129 +8567,129 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr">
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I161" s="6" t="inlineStr">
+      <c r="I161" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9710,215 +9730,215 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10959,215 +10979,215 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
+      <c r="H213" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
+      <c r="H214" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
+      <c r="H217" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12208,215 +12228,215 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr"/>
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I240" s="6" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr"/>
-      <c r="H241" s="6" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13363,43 +13383,43 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr"/>
+      <c r="H265" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13453,215 +13473,215 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr"/>
+      <c r="H267" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
+      <c r="I268" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14702,215 +14722,215 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="6" t="inlineStr">
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="6" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr"/>
+      <c r="H295" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15105,43 +15125,43 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
+      <c r="A303" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="9" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C303" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="5" t="inlineStr">
+      <c r="C303" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="5" t="inlineStr">
+      <c r="E303" s="9" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F303" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="5" t="inlineStr"/>
-      <c r="H303" s="5" t="inlineStr">
+      <c r="F303" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="9" t="inlineStr"/>
+      <c r="H303" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I303" s="5" t="inlineStr">
+      <c r="I303" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15947,215 +15967,215 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr"/>
+      <c r="H321" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr"/>
+      <c r="H325" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1837,10 +1837,10 @@
         <v>24</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         <v>24</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>24</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         <v>23</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         <v>24</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         <v>23</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9824,45 +9824,45 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="9" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C188" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="9" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E188" s="9" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F188" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="9" t="inlineStr"/>
-      <c r="H188" s="9" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I188" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11081,45 +11081,45 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="9" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C215" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E215" s="9" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F215" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="9" t="inlineStr"/>
-      <c r="H215" s="9" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I215" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12338,45 +12338,45 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="9" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C242" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="9" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E242" s="9" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F242" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="9" t="inlineStr"/>
-      <c r="H242" s="9" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I242" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13591,45 +13591,45 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="9" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C269" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="9" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E269" s="9" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F269" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="9" t="inlineStr"/>
-      <c r="H269" s="9" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I269" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I269" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14848,45 +14848,45 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="9" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C296" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="9" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E296" s="9" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F296" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="9" t="inlineStr"/>
-      <c r="H296" s="9" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I296" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I296" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -16101,45 +16101,45 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="9" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C323" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="9" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E323" s="9" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F323" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="9" t="inlineStr"/>
-      <c r="H323" s="9" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I323" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I323" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
